--- a/outputs/01a0719b-f374-7590-b5ae-261ff64e352b/working_papers.xlsx
+++ b/outputs/01a0719b-f374-7590-b5ae-261ff64e352b/working_papers.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working papers" sheetId="1" r:id="R79bb8b2788af48b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working papers" sheetId="1" r:id="Re27f88cb6dfd4713"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -755,7 +755,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1f2cb893e5f4cb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47ee021dae994e53"/>
   </x:tableParts>
 </x:worksheet>
 </file>